--- a/data/trans_orig/P1421-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2007</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>30857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>24761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449254</t>
+          <t>449515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465112</t>
+          <t>464327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276799</t>
+          <t>275823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294099</t>
+          <t>293685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731792</t>
+          <t>731167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755414</t>
+          <t>755696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41608</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351629</t>
+          <t>350979</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363039</t>
+          <t>363083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330257</t>
+          <t>330756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351457</t>
+          <t>351608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687918</t>
+          <t>686635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710570</t>
+          <t>710746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24206</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518183</t>
+          <t>518847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533513</t>
+          <t>533985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147975</t>
+          <t>147187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161142</t>
+          <t>161503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671247</t>
+          <t>671283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>691669</t>
+          <t>692394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41200</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58834</t>
+          <t>60165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57504</t>
+          <t>57001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91092</t>
+          <t>93963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1197134</t>
+          <t>1197393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1220216</t>
+          <t>1218676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655451</t>
+          <t>654120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681335</t>
+          <t>681516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1861528</t>
+          <t>1858657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895116</t>
+          <t>1895619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42923</t>
+          <t>43838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27852</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53523</t>
+          <t>55078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333630</t>
+          <t>333253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346243</t>
+          <t>346224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>525829</t>
+          <t>524914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>547456</t>
+          <t>547941</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865784</t>
+          <t>864229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>891455</t>
+          <t>890780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>43101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>72157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>46109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73806</t>
+          <t>75428</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290458</t>
+          <t>289954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297356</t>
+          <t>297349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1177627</t>
+          <t>1176603</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1204657</t>
+          <t>1205659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1473154</t>
+          <t>1471532</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1501828</t>
+          <t>1500851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>62000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95142</t>
+          <t>98579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168967</t>
+          <t>169732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222399</t>
+          <t>223849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240097</t>
+          <t>245020</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304442</t>
+          <t>304844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3175048</t>
+          <t>3171611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208497</t>
+          <t>3208190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3155725</t>
+          <t>3154275</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3209157</t>
+          <t>3208392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6343872</t>
+          <t>6343470</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6408217</t>
+          <t>6403294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2012</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>32336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16789</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37342</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425788</t>
+          <t>426426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280904</t>
+          <t>282118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299487</t>
+          <t>300040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714323</t>
+          <t>714173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734876</t>
+          <t>735035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>31549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408938</t>
+          <t>408516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417784</t>
+          <t>417765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312143</t>
+          <t>312458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328867</t>
+          <t>329031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726579</t>
+          <t>725259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744983</t>
+          <t>744173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611570</t>
+          <t>612870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624316</t>
+          <t>624442</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235565</t>
+          <t>235728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251418</t>
+          <t>252187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853970</t>
+          <t>853045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>873350</t>
+          <t>873325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>27651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>52083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41835</t>
+          <t>40462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71781</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133412</t>
+          <t>1133295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1150089</t>
+          <t>1149320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711663</t>
+          <t>712639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736773</t>
+          <t>737071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1851950</t>
+          <t>1851277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1881896</t>
+          <t>1883269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37442</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42163</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>70386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498785</t>
+          <t>499126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508272</t>
+          <t>508627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694345</t>
+          <t>694038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722804</t>
+          <t>722653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1200127</t>
+          <t>1200457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1228680</t>
+          <t>1228958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34513</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62271</t>
+          <t>61830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67679</t>
+          <t>66637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258388</t>
+          <t>257292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265932</t>
+          <t>265924</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1047080</t>
+          <t>1047521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074838</t>
+          <t>1074630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1308554</t>
+          <t>1309596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1338083</t>
+          <t>1338766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57722</t>
+          <t>56498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161977</t>
+          <t>162622</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218022</t>
+          <t>216076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202459</t>
+          <t>203746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262849</t>
+          <t>265577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3363158</t>
+          <t>3364382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3390971</t>
+          <t>3391388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3328893</t>
+          <t>3330839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3384938</t>
+          <t>3384293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6704945</t>
+          <t>6702217</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6765335</t>
+          <t>6764048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2016</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36057</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407172</t>
+          <t>406572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422110</t>
+          <t>421966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326251</t>
+          <t>324952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340411</t>
+          <t>340438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740090</t>
+          <t>738802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759410</t>
+          <t>759085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>29707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368914</t>
+          <t>368392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376301</t>
+          <t>376304</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341456</t>
+          <t>342566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361189</t>
+          <t>360420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714852</t>
+          <t>715289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735289</t>
+          <t>734985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511442</t>
+          <t>511490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520792</t>
+          <t>520761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>145376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159501</t>
+          <t>159713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660785</t>
+          <t>661990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678162</t>
+          <t>678468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31781</t>
+          <t>30873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>67395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1130519</t>
+          <t>1130002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144753</t>
+          <t>1144915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>768855</t>
+          <t>769224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>794095</t>
+          <t>795003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907586</t>
+          <t>1908119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1935694</t>
+          <t>1936839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70141</t>
+          <t>70291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54817</t>
+          <t>50993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88060</t>
+          <t>84557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>597252</t>
+          <t>597353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612457</t>
+          <t>612070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>668103</t>
+          <t>667953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697937</t>
+          <t>698500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1270890</t>
+          <t>1274393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1304133</t>
+          <t>1307957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39626</t>
+          <t>40986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69240</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>40764</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>70826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279990</t>
+          <t>279955</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1012785</t>
+          <t>1012342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1042399</t>
+          <t>1041039</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1298017</t>
+          <t>1298344</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1328337</t>
+          <t>1328406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>35466</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63442</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167960</t>
+          <t>167639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221212</t>
+          <t>224112</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213083</t>
+          <t>211955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274186</t>
+          <t>274572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3322280</t>
+          <t>3321718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3350693</t>
+          <t>3350256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3310384</t>
+          <t>3307484</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3363636</t>
+          <t>3363957</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6643132</t>
+          <t>6642746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6704235</t>
+          <t>6705363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2023</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54825</t>
+          <t>53541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54305</t>
+          <t>54994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>83339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466212</t>
+          <t>467878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487213</t>
+          <t>487388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>392642</t>
+          <t>393926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414441</t>
+          <t>414965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>868753</t>
+          <t>869340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>898374</t>
+          <t>897685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>70885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428365</t>
+          <t>427649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443607</t>
+          <t>443467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329543</t>
+          <t>329834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349265</t>
+          <t>349450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>762856</t>
+          <t>763239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789287</t>
+          <t>789159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67567</t>
+          <t>67804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630283</t>
+          <t>628079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661410</t>
+          <t>661847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135939</t>
+          <t>136565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149885</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>766889</t>
+          <t>766652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817319</t>
+          <t>817226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36807</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>66034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>49211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125115</t>
+          <t>123923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99504</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168886</t>
+          <t>168732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970096</t>
+          <t>968785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>998012</t>
+          <t>998635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>852979</t>
+          <t>854171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>931329</t>
+          <t>928883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1844026</t>
+          <t>1844180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1913408</t>
+          <t>1914118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75823</t>
+          <t>78980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126140</t>
+          <t>125990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103796</t>
+          <t>102100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153694</t>
+          <t>152525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434866</t>
+          <t>436043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456816</t>
+          <t>457462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711430</t>
+          <t>711580</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>761747</t>
+          <t>758590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1157760</t>
+          <t>1158929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207658</t>
+          <t>1209354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56175</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87195</t>
+          <t>84202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61218</t>
+          <t>60225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93406</t>
+          <t>94820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224537</t>
+          <t>222427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237951</t>
+          <t>237868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>672163</t>
+          <t>675156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703183</t>
+          <t>705069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>906459</t>
+          <t>905045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>938647</t>
+          <t>939640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107288</t>
+          <t>112325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172626</t>
+          <t>170114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>303827</t>
+          <t>302748</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>418611</t>
+          <t>410584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443539</t>
+          <t>447284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>572943</t>
+          <t>570279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3201554</t>
+          <t>3204066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3266892</t>
+          <t>3261855</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3152700</t>
+          <t>3160727</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3267484</t>
+          <t>3268563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6372548</t>
+          <t>6375212</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6501952</t>
+          <t>6498207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1421-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24261</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>33097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449515</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464327</t>
+          <t>465147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275823</t>
+          <t>273583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293685</t>
+          <t>293171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731167</t>
+          <t>732738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755696</t>
+          <t>756067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350979</t>
+          <t>351646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363083</t>
+          <t>363037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330756</t>
+          <t>330744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351608</t>
+          <t>351416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686635</t>
+          <t>687246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710746</t>
+          <t>710855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23542</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>39035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518847</t>
+          <t>518778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533985</t>
+          <t>533897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147187</t>
+          <t>147921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161503</t>
+          <t>161486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671283</t>
+          <t>671136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692394</t>
+          <t>691934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>32325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60165</t>
+          <t>57442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57001</t>
+          <t>57261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93963</t>
+          <t>91382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1197393</t>
+          <t>1197766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1218676</t>
+          <t>1219024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654120</t>
+          <t>656843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681516</t>
+          <t>681960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1858657</t>
+          <t>1861238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895619</t>
+          <t>1895359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>44027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55078</t>
+          <t>54947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333253</t>
+          <t>333418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346224</t>
+          <t>346393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>524914</t>
+          <t>524725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>547941</t>
+          <t>546486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>864229</t>
+          <t>864360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890780</t>
+          <t>891097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43101</t>
+          <t>43958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72157</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>75645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289954</t>
+          <t>290348</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297349</t>
+          <t>297351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1176603</t>
+          <t>1176037</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1205659</t>
+          <t>1204802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1471532</t>
+          <t>1471315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1500851</t>
+          <t>1501795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62000</t>
+          <t>62055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98579</t>
+          <t>99086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169732</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223849</t>
+          <t>222963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245020</t>
+          <t>243098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304844</t>
+          <t>304858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3171611</t>
+          <t>3171104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3208190</t>
+          <t>3208135</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3154275</t>
+          <t>3155161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3208392</t>
+          <t>3212173</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6343470</t>
+          <t>6343456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6403294</t>
+          <t>6405216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426426</t>
+          <t>424507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282118</t>
+          <t>281281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300040</t>
+          <t>299972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714173</t>
+          <t>713977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>735035</t>
+          <t>734732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>31802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408516</t>
+          <t>407951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417765</t>
+          <t>417654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312458</t>
+          <t>312629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329031</t>
+          <t>329209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725259</t>
+          <t>725006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744173</t>
+          <t>745091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612870</t>
+          <t>612128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624442</t>
+          <t>623749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235728</t>
+          <t>236010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252187</t>
+          <t>251348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853045</t>
+          <t>854060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>873325</t>
+          <t>873248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27651</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>55528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40462</t>
+          <t>41148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72454</t>
+          <t>70708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133295</t>
+          <t>1133686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1149320</t>
+          <t>1149401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712639</t>
+          <t>709194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737071</t>
+          <t>736161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1851277</t>
+          <t>1853023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1883269</t>
+          <t>1882583</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37593</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66208</t>
+          <t>64384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70386</t>
+          <t>70104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499126</t>
+          <t>498054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508627</t>
+          <t>508468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694038</t>
+          <t>695862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722653</t>
+          <t>724029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1200457</t>
+          <t>1200739</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1228958</t>
+          <t>1228869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61830</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66637</t>
+          <t>64240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257292</t>
+          <t>257674</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265924</t>
+          <t>265927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1047521</t>
+          <t>1045514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074630</t>
+          <t>1075428</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1309596</t>
+          <t>1311993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1338766</t>
+          <t>1339407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>57090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162622</t>
+          <t>163897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216076</t>
+          <t>218186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203746</t>
+          <t>200729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265577</t>
+          <t>260164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3364382</t>
+          <t>3363790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3391388</t>
+          <t>3390801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3330839</t>
+          <t>3328729</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3384293</t>
+          <t>3383018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6702217</t>
+          <t>6707630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6764048</t>
+          <t>6767065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406572</t>
+          <t>407587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421966</t>
+          <t>421386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324952</t>
+          <t>325692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340438</t>
+          <t>340159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738802</t>
+          <t>737962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759085</t>
+          <t>759180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>30730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34211</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368392</t>
+          <t>369169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376304</t>
+          <t>376289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342566</t>
+          <t>341543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360420</t>
+          <t>360606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715289</t>
+          <t>715688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734985</t>
+          <t>735970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511490</t>
+          <t>511559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520761</t>
+          <t>520778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145376</t>
+          <t>144645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>159537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>661990</t>
+          <t>661522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678468</t>
+          <t>678222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30873</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>56231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67395</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1130002</t>
+          <t>1130333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144915</t>
+          <t>1144483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>769224</t>
+          <t>769645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>795003</t>
+          <t>795043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1908119</t>
+          <t>1906636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1936839</t>
+          <t>1936142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>24921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70291</t>
+          <t>69854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50993</t>
+          <t>52587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84557</t>
+          <t>88487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>597353</t>
+          <t>595785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612070</t>
+          <t>611945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>667953</t>
+          <t>668390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>698500</t>
+          <t>697771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274393</t>
+          <t>1270463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1307957</t>
+          <t>1306363</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40764</t>
+          <t>41561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70826</t>
+          <t>71768</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279955</t>
+          <t>280655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1012342</t>
+          <t>1013147</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1041039</t>
+          <t>1042572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1298344</t>
+          <t>1297402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1328406</t>
+          <t>1327609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35466</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>63129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167639</t>
+          <t>168587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>224112</t>
+          <t>225056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211955</t>
+          <t>208646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274572</t>
+          <t>270738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3321718</t>
+          <t>3322593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3350256</t>
+          <t>3349638</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3307484</t>
+          <t>3306540</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3363957</t>
+          <t>3363009</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6642746</t>
+          <t>6646580</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6705363</t>
+          <t>6708672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,22 +8668,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42509</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>73825</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>60307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83339</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>478789</t>
+          <t>522991</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467878</t>
+          <t>511828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487388</t>
+          <t>532448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,27 +8781,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>404958</t>
+          <t>442213</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393926</t>
+          <t>429090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414965</t>
+          <t>452932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>883748</t>
+          <t>965204</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869340</t>
+          <t>947005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>897685</t>
+          <t>978722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41288</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32461</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>57723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>61527</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44965</t>
+          <t>48883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70885</t>
+          <t>76142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>436916</t>
+          <t>467211</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427649</t>
+          <t>457760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443467</t>
+          <t>473992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>340623</t>
+          <t>376966</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329834</t>
+          <t>364769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349450</t>
+          <t>386074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>777539</t>
+          <t>844177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>763239</t>
+          <t>829562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789159</t>
+          <t>856821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43744</t>
+          <t>48937</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>62601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>647125</t>
+          <t>448598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628079</t>
+          <t>435577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661847</t>
+          <t>457168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>143587</t>
+          <t>160705</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136565</t>
+          <t>152160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>167890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>790712</t>
+          <t>609304</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>766652</t>
+          <t>595640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817226</t>
+          <t>621287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49064</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66034</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92081</t>
+          <t>103887</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>89012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123923</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141144</t>
+          <t>155215</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98794</t>
+          <t>134584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168732</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>985755</t>
+          <t>1080515</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>968785</t>
+          <t>1065157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>998635</t>
+          <t>1093963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>886013</t>
+          <t>757324</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>854171</t>
+          <t>737924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>928883</t>
+          <t>772199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1871768</t>
+          <t>1837839</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1844180</t>
+          <t>1812419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914118</t>
+          <t>1858470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37841</t>
+          <t>41598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>110227</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78980</t>
+          <t>95562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125990</t>
+          <t>126706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>128393</t>
+          <t>137934</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102100</t>
+          <t>120032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152525</t>
+          <t>157803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>448106</t>
+          <t>537531</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436043</t>
+          <t>523640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457462</t>
+          <t>547126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>734956</t>
+          <t>718388</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711580</t>
+          <t>701909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>758590</t>
+          <t>733053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1183061</t>
+          <t>1255919</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1158929</t>
+          <t>1236050</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209354</t>
+          <t>1273821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473884</t>
+          <t>565238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473884</t>
+          <t>565238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473884</t>
+          <t>565238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837570</t>
+          <t>828615</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837570</t>
+          <t>828615</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837570</t>
+          <t>828615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1311454</t>
+          <t>1393853</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1311454</t>
+          <t>1393853</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1311454</t>
+          <t>1393853</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>73398</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54289</t>
+          <t>58867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84202</t>
+          <t>90512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>75669</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60225</t>
+          <t>64555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94820</t>
+          <t>97855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>233534</t>
+          <t>230097</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222427</t>
+          <t>220022</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237868</t>
+          <t>234767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>690662</t>
+          <t>768830</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>675156</t>
+          <t>751716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>705069</t>
+          <t>783361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>924196</t>
+          <t>998926</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>905045</t>
+          <t>981600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939640</t>
+          <t>1014900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759358</t>
+          <t>842228</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759358</t>
+          <t>842228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759358</t>
+          <t>842228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999865</t>
+          <t>1079455</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999865</t>
+          <t>1079455</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999865</t>
+          <t>1079455</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>143955</t>
+          <t>151938</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>129423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170114</t>
+          <t>180374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>370512</t>
+          <t>406028</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>302748</t>
+          <t>372584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>410584</t>
+          <t>441661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>514467</t>
+          <t>557966</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>447284</t>
+          <t>509402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>570279</t>
+          <t>599968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3230225</t>
+          <t>3286944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3204066</t>
+          <t>3258508</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3261855</t>
+          <t>3309459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3200799</t>
+          <t>3224425</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3160727</t>
+          <t>3188792</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3268563</t>
+          <t>3257869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6431024</t>
+          <t>6511370</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6375212</t>
+          <t>6469368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6498207</t>
+          <t>6559934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374180</t>
+          <t>3438882</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374180</t>
+          <t>3438882</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374180</t>
+          <t>3438882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571311</t>
+          <t>3630453</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571311</t>
+          <t>3630453</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571311</t>
+          <t>3630453</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6945491</t>
+          <t>7069336</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6945491</t>
+          <t>7069336</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6945491</t>
+          <t>7069336</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
